--- a/data/probes/bacteria_probes.xlsx
+++ b/data/probes/bacteria_probes.xlsx
@@ -49,7 +49,7 @@
     <t>hyb_region_right</t>
   </si>
   <si>
-    <t>combined_probe</t>
+    <t>hyb_region_full</t>
   </si>
   <si>
     <t>Alistipes_finegoldii_consensus_probe1</t>
